--- a/3_CGE/Game_theory_2024/5_Visualisation/Viz_Results_Brazil_Detailed_Results_EQ.xlsx
+++ b/3_CGE/Game_theory_2024/5_Visualisation/Viz_Results_Brazil_Detailed_Results_EQ.xlsx
@@ -373,7 +373,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -382,22 +382,16 @@
         </is>
       </c>
       <c r="C2" s="0">
-        <v>4056.576171875</v>
-      </c>
-      <c r="D2" s="0">
-        <v>27970.1640625</v>
-      </c>
-      <c r="E2" s="0">
-        <v>32026.7408346344</v>
+        <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>12.666216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -406,22 +400,16 @@
         </is>
       </c>
       <c r="C3" s="0">
-        <v>270.112487792969</v>
-      </c>
-      <c r="D3" s="0">
-        <v>1518.59265136719</v>
-      </c>
-      <c r="E3" s="0">
-        <v>1788.70513597516</v>
+        <v>0</v>
       </c>
       <c r="F3" s="0">
-        <v>15.101007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -430,22 +418,16 @@
         </is>
       </c>
       <c r="C4" s="0">
-        <v>18.6912002563477</v>
-      </c>
-      <c r="D4" s="0">
-        <v>112.337699890137</v>
-      </c>
-      <c r="E4" s="0">
-        <v>131.028898158021</v>
+        <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>14.264945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -454,22 +436,16 @@
         </is>
       </c>
       <c r="C5" s="0">
-        <v>-26566.3125</v>
-      </c>
-      <c r="D5" s="0">
-        <v>339876.15625</v>
-      </c>
-      <c r="E5" s="0">
-        <v>313309.845002728</v>
+        <v>0</v>
       </c>
       <c r="F5" s="0">
-        <v>-8.479246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -478,22 +454,16 @@
         </is>
       </c>
       <c r="C6" s="0">
-        <v>44667.91015625</v>
-      </c>
-      <c r="D6" s="0">
-        <v>601544.9375</v>
-      </c>
-      <c r="E6" s="0">
-        <v>646212.818329316</v>
+        <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>6.91226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -502,22 +472,16 @@
         </is>
       </c>
       <c r="C7" s="0">
-        <v>6258.48828125</v>
-      </c>
-      <c r="D7" s="0">
-        <v>36044.1171875</v>
-      </c>
-      <c r="E7" s="0">
-        <v>42302.6063229689</v>
+        <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>14.794569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -526,22 +490,22 @@
         </is>
       </c>
       <c r="C8" s="0">
-        <v>465.156890869141</v>
+        <v>30169.5</v>
       </c>
       <c r="D8" s="0">
-        <v>5204.06396484375</v>
+        <v>120560.4296875</v>
       </c>
       <c r="E8" s="0">
-        <v>5669.22066304512</v>
+        <v>150729.93065409</v>
       </c>
       <c r="F8" s="0">
-        <v>8.204953</v>
+        <v>20.0156</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -550,1624 +514,3496 @@
         </is>
       </c>
       <c r="C9" s="0">
-        <v>60.1967010498047</v>
+        <v>974.299987792969</v>
       </c>
       <c r="D9" s="0">
-        <v>466.545043945313</v>
+        <v>11084.763671875</v>
       </c>
       <c r="E9" s="0">
-        <v>526.741756125543</v>
+        <v>12059.0636407774</v>
       </c>
       <c r="F9" s="0">
-        <v>11.428124</v>
+        <v>8.0794</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cattle</t>
+          <t>c_b</t>
         </is>
       </c>
       <c r="C10" s="0">
-        <v>-325000</v>
+        <v>308.200012207031</v>
       </c>
       <c r="D10" s="0">
-        <v>19111128</v>
+        <v>1923.09619140625</v>
       </c>
       <c r="E10" s="0">
-        <v>18786127.1676301</v>
+        <v>2231.29615139099</v>
       </c>
       <c r="F10" s="0">
-        <v>-1.73</v>
+        <v>13.8126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cattle</t>
+          <t>c_b</t>
         </is>
       </c>
       <c r="C11" s="0">
-        <v>-4060</v>
-      </c>
-      <c r="D11" s="0">
-        <v>1615171.125</v>
-      </c>
-      <c r="E11" s="0">
-        <v>1611111.11111111</v>
+        <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>-0.252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cattle</t>
+          <t>c_b</t>
         </is>
       </c>
       <c r="C12" s="0">
-        <v>-60</v>
-      </c>
-      <c r="D12" s="0">
-        <v>19540.51953125</v>
-      </c>
-      <c r="E12" s="0">
-        <v>19480.5194805195</v>
+        <v>0</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cattle</t>
+          <t>c_b</t>
         </is>
       </c>
       <c r="C13" s="0">
-        <v>-1557000</v>
-      </c>
-      <c r="D13" s="0">
-        <v>26115360</v>
-      </c>
-      <c r="E13" s="0">
-        <v>24558359.6214511</v>
+        <v>0</v>
       </c>
       <c r="F13" s="0">
-        <v>-6.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cattle</t>
+          <t>c_b</t>
         </is>
       </c>
       <c r="C14" s="0">
-        <v>-2849000</v>
+        <v>-306798</v>
       </c>
       <c r="D14" s="0">
-        <v>103165904</v>
+        <v>2616710.75</v>
       </c>
       <c r="E14" s="0">
-        <v>100316901.408451</v>
+        <v>2309912.81302233</v>
       </c>
       <c r="F14" s="0">
-        <v>-2.84</v>
+        <v>-13.2818</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cattle</t>
+          <t>c_b</t>
         </is>
       </c>
       <c r="C15" s="0">
-        <v>-603000</v>
+        <v>428169.1875</v>
       </c>
       <c r="D15" s="0">
-        <v>19505822</v>
+        <v>5035123.5</v>
       </c>
       <c r="E15" s="0">
-        <v>18902821.3166144</v>
+        <v>5463292.85331496</v>
       </c>
       <c r="F15" s="0">
-        <v>-3.19</v>
+        <v>7.8372</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cattle</t>
+          <t>c_b</t>
         </is>
       </c>
       <c r="C16" s="0">
-        <v>-108</v>
+        <v>132868.5</v>
       </c>
       <c r="D16" s="0">
-        <v>5400108</v>
+        <v>1799764.25</v>
       </c>
       <c r="E16" s="0">
-        <v>5400000</v>
+        <v>1932632.72727273</v>
       </c>
       <c r="F16" s="0">
-        <v>-0.002</v>
+        <v>6.875</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cattle</t>
+          <t>c_b</t>
         </is>
       </c>
       <c r="C17" s="0">
-        <v>-2620</v>
+        <v>8980.400390625</v>
       </c>
       <c r="D17" s="0">
-        <v>347811.03125</v>
+        <v>163620.03125</v>
       </c>
       <c r="E17" s="0">
-        <v>345191.040843215</v>
+        <v>172600.430340669</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.759</v>
+        <v>5.203</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>c_b</t>
         </is>
       </c>
       <c r="C18" s="0">
-        <v>756000</v>
+        <v>6690.10009765625</v>
       </c>
       <c r="D18" s="0">
-        <v>6583806</v>
+        <v>28062.583984375</v>
       </c>
       <c r="E18" s="0">
-        <v>7339805.82524272</v>
+        <v>34752.6835405455</v>
       </c>
       <c r="F18" s="0">
-        <v>10.3</v>
+        <v>19.2506</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>c_b</t>
         </is>
       </c>
       <c r="C19" s="0">
-        <v>2153000</v>
+        <v>2861.39990234375</v>
       </c>
       <c r="D19" s="0">
-        <v>99403600</v>
+        <v>11394.705078125</v>
       </c>
       <c r="E19" s="0">
-        <v>101556603.773585</v>
+        <v>14256.1052160973</v>
       </c>
       <c r="F19" s="0">
-        <v>2.12</v>
+        <v>20.0714</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C20" s="0">
-        <v>3399000</v>
-      </c>
-      <c r="D20" s="0">
-        <v>35226000</v>
-      </c>
-      <c r="E20" s="0">
-        <v>38625000</v>
+        <v>0</v>
       </c>
       <c r="F20" s="0">
-        <v>8.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C21" s="0">
-        <v>608000</v>
-      </c>
-      <c r="D21" s="0">
-        <v>5583446</v>
-      </c>
-      <c r="E21" s="0">
-        <v>6191446.02851324</v>
+        <v>0</v>
       </c>
       <c r="F21" s="0">
-        <v>9.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gro</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C22" s="0">
-        <v>-10242.0732421875</v>
-      </c>
-      <c r="D22" s="0">
-        <v>597512.5625</v>
-      </c>
-      <c r="E22" s="0">
-        <v>587270.464279079</v>
+        <v>0</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.744013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gro</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C23" s="0">
-        <v>565.436584472656</v>
-      </c>
-      <c r="D23" s="0">
-        <v>21487.05859375</v>
-      </c>
-      <c r="E23" s="0">
-        <v>22052.49607155</v>
+        <v>0</v>
       </c>
       <c r="F23" s="0">
-        <v>2.564048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gro</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C24" s="0">
-        <v>1.13940000534058</v>
-      </c>
-      <c r="D24" s="0">
-        <v>61.4976577758789</v>
-      </c>
-      <c r="E24" s="0">
-        <v>62.6370566488007</v>
+        <v>0</v>
       </c>
       <c r="F24" s="0">
-        <v>1.819051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gro</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C25" s="0">
-        <v>-8711.7578125</v>
-      </c>
-      <c r="D25" s="0">
-        <v>311038.75</v>
-      </c>
-      <c r="E25" s="0">
-        <v>302326.990461443</v>
+        <v>0</v>
       </c>
       <c r="F25" s="0">
-        <v>-2.881568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>gro</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C26" s="0">
-        <v>-20432.74609375</v>
+        <v>-97924.3984375</v>
       </c>
       <c r="D26" s="0">
-        <v>515479.34375</v>
+        <v>15071074</v>
       </c>
       <c r="E26" s="0">
-        <v>495046.591694026</v>
+        <v>14973149.6081804</v>
       </c>
       <c r="F26" s="0">
-        <v>-4.127439</v>
+        <v>-0.654</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gro</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C27" s="0">
-        <v>-3158.67065429688</v>
+        <v>-37</v>
       </c>
       <c r="D27" s="0">
-        <v>179105.65625</v>
+        <v>156816.65625</v>
       </c>
       <c r="E27" s="0">
-        <v>175946.985043608</v>
+        <v>156779.661016949</v>
       </c>
       <c r="F27" s="0">
-        <v>-1.79524</v>
+        <v>-0.0236</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gro</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C28" s="0">
-        <v>-148.558395385742</v>
+        <v>-205.100006103516</v>
       </c>
       <c r="D28" s="0">
-        <v>80890.328125</v>
+        <v>638.202453613281</v>
       </c>
       <c r="E28" s="0">
-        <v>80741.7688735066</v>
+        <v>433.102470866449</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.183992</v>
+        <v>-47.356</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gro</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C29" s="0">
-        <v>-29.5044002532959</v>
-      </c>
-      <c r="D29" s="0">
-        <v>4192.18896484375</v>
-      </c>
-      <c r="E29" s="0">
-        <v>4162.68452450128</v>
+        <v>0</v>
       </c>
       <c r="F29" s="0">
-        <v>-0.708783</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ocr</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C30" s="0">
-        <v>216.270095825195</v>
-      </c>
-      <c r="D30" s="0">
-        <v>64912.37890625</v>
-      </c>
-      <c r="E30" s="0">
-        <v>65128.647866748</v>
+        <v>0</v>
       </c>
       <c r="F30" s="0">
-        <v>0.332066</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ocr</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C31" s="0">
-        <v>-1076.13806152344</v>
-      </c>
-      <c r="D31" s="0">
-        <v>22913.22265625</v>
-      </c>
-      <c r="E31" s="0">
-        <v>21837.0842207421</v>
+        <v>0</v>
       </c>
       <c r="F31" s="0">
-        <v>-4.92803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ocr</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C32" s="0">
-        <v>-39.5909996032715</v>
+        <v>-1886524.5</v>
       </c>
       <c r="D32" s="0">
-        <v>744.2314453125</v>
+        <v>33500368</v>
       </c>
       <c r="E32" s="0">
-        <v>704.640464514737</v>
+        <v>31613843.5499548</v>
       </c>
       <c r="F32" s="0">
-        <v>-5.61861</v>
+        <v>-5.9674</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ocr</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C33" s="0">
-        <v>-1114.13342285156</v>
+        <v>-2231098</v>
       </c>
       <c r="D33" s="0">
-        <v>96367.140625</v>
+        <v>77738680</v>
       </c>
       <c r="E33" s="0">
-        <v>95253.0034746565</v>
+        <v>75507580.8853391</v>
       </c>
       <c r="F33" s="0">
-        <v>-1.169657</v>
+        <v>-2.9548</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ocr</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C34" s="0">
-        <v>217.821197509766</v>
+        <v>-740806</v>
       </c>
       <c r="D34" s="0">
-        <v>118779.59375</v>
+        <v>37782960</v>
       </c>
       <c r="E34" s="0">
-        <v>118997.414603772</v>
+        <v>37042152.1076054</v>
       </c>
       <c r="F34" s="0">
-        <v>0.183047</v>
+        <v>-1.9999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ocr</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C35" s="0">
-        <v>33.9648017883301</v>
+        <v>-173.199996948242</v>
       </c>
       <c r="D35" s="0">
-        <v>16872.779296875</v>
+        <v>7872900.5</v>
       </c>
       <c r="E35" s="0">
-        <v>16906.7432182633</v>
+        <v>7872727.13401101</v>
       </c>
       <c r="F35" s="0">
-        <v>0.200895</v>
+        <v>-0.0022</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ocr</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C36" s="0">
-        <v>0.144999995827675</v>
+        <v>-81371.8984375</v>
       </c>
       <c r="D36" s="0">
-        <v>2019.072265625</v>
+        <v>681747.4375</v>
       </c>
       <c r="E36" s="0">
-        <v>2019.21732109281</v>
+        <v>600375.537222858</v>
       </c>
       <c r="F36" s="0">
-        <v>0.007181</v>
+        <v>-13.5535</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ocr</t>
+          <t>Cattle</t>
         </is>
       </c>
       <c r="C37" s="0">
-        <v>-1.37000000104308e-02</v>
+        <v>-5394.89990234375</v>
       </c>
       <c r="D37" s="0">
-        <v>0.185771942138672</v>
+        <v>136034.671875</v>
       </c>
       <c r="E37" s="0">
-        <v>0.172071944792674</v>
+        <v>130639.769041644</v>
       </c>
       <c r="F37" s="0">
-        <v>-7.961786</v>
+        <v>-4.1296</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>osd</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C38" s="0">
-        <v>-33204.05078125</v>
-      </c>
-      <c r="D38" s="0">
-        <v>1070557</v>
-      </c>
-      <c r="E38" s="0">
-        <v>1037352.98506425</v>
+        <v>0</v>
       </c>
       <c r="F38" s="0">
-        <v>-3.200844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>osd</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C39" s="0">
-        <v>-46.7240982055664</v>
-      </c>
-      <c r="D39" s="0">
-        <v>2560.63623046875</v>
-      </c>
-      <c r="E39" s="0">
-        <v>2513.91209964626</v>
+        <v>0</v>
       </c>
       <c r="F39" s="0">
-        <v>-1.858621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>osd</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C40" s="0">
-        <v>-0.352800011634827</v>
-      </c>
-      <c r="D40" s="0">
-        <v>14.0725364685059</v>
-      </c>
-      <c r="E40" s="0">
-        <v>13.7197367286373</v>
+        <v>0</v>
       </c>
       <c r="F40" s="0">
-        <v>-2.571478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>osd</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C41" s="0">
-        <v>-15339.0625</v>
-      </c>
-      <c r="D41" s="0">
-        <v>498735.46875</v>
-      </c>
-      <c r="E41" s="0">
-        <v>483396.41401305</v>
+        <v>0</v>
       </c>
       <c r="F41" s="0">
-        <v>-3.173185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>osd</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C42" s="0">
-        <v>-73312.0703125</v>
-      </c>
-      <c r="D42" s="0">
-        <v>1434928.5</v>
-      </c>
-      <c r="E42" s="0">
-        <v>1361616.43344389</v>
+        <v>0</v>
       </c>
       <c r="F42" s="0">
-        <v>-5.384194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>osd</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C43" s="0">
-        <v>-4828.34765625</v>
-      </c>
-      <c r="D43" s="0">
-        <v>211683.265625</v>
-      </c>
-      <c r="E43" s="0">
-        <v>206854.924350015</v>
+        <v>0</v>
       </c>
       <c r="F43" s="0">
-        <v>-2.334171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>osd</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C44" s="0">
-        <v>-52.6054992675781</v>
+        <v>654810.1875</v>
       </c>
       <c r="D44" s="0">
-        <v>12366.88671875</v>
+        <v>4425846</v>
       </c>
       <c r="E44" s="0">
-        <v>12314.2807942064</v>
+        <v>5080656.00195526</v>
       </c>
       <c r="F44" s="0">
-        <v>-0.427191</v>
+        <v>12.8883</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>osd</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C45" s="0">
-        <v>-27.4624004364014</v>
-      </c>
-      <c r="D45" s="0">
-        <v>577.891723632813</v>
-      </c>
-      <c r="E45" s="0">
-        <v>550.429340177917</v>
+        <v>0</v>
       </c>
       <c r="F45" s="0">
-        <v>-4.989269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ8</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pdr</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C46" s="0">
-        <v>5192.12890625</v>
-      </c>
-      <c r="D46" s="0">
-        <v>86676.171875</v>
-      </c>
-      <c r="E46" s="0">
-        <v>91868.2987084084</v>
+        <v>0</v>
       </c>
       <c r="F46" s="0">
-        <v>5.651709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pdr</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C47" s="0">
-        <v>61.2667999267578</v>
-      </c>
-      <c r="D47" s="0">
-        <v>710.850830078125</v>
-      </c>
-      <c r="E47" s="0">
-        <v>772.117623673602</v>
+        <v>0</v>
       </c>
       <c r="F47" s="0">
-        <v>7.934905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pdr</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C48" s="0">
-        <v>0.419400006532669</v>
+        <v>2714409.75</v>
       </c>
       <c r="D48" s="0">
-        <v>5.4455943107605</v>
+        <v>102377144</v>
       </c>
       <c r="E48" s="0">
-        <v>5.86499446549077</v>
+        <v>105091554.067134</v>
       </c>
       <c r="F48" s="0">
-        <v>7.150902</v>
+        <v>2.5829</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>pdr</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C49" s="0">
-        <v>-3019.95947265625</v>
+        <v>2908566</v>
       </c>
       <c r="D49" s="0">
-        <v>24321.412109375</v>
+        <v>32730384</v>
       </c>
       <c r="E49" s="0">
-        <v>21301.4520566387</v>
+        <v>35638950.1543891</v>
       </c>
       <c r="F49" s="0">
-        <v>-14.177247</v>
+        <v>8.1612</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>pdr</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="C50" s="0">
-        <v>208.776794433594</v>
+        <v>715554.3125</v>
       </c>
       <c r="D50" s="0">
-        <v>81344.34375</v>
+        <v>6760877.5</v>
       </c>
       <c r="E50" s="0">
-        <v>81553.1167587602</v>
+        <v>7476431.56789401</v>
       </c>
       <c r="F50" s="0">
-        <v>0.256001</v>
+        <v>9.5708</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pdr</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C51" s="0">
-        <v>2650.81665039063</v>
-      </c>
-      <c r="D51" s="0">
-        <v>32011.44140625</v>
-      </c>
-      <c r="E51" s="0">
-        <v>34662.2582498628</v>
+        <v>0</v>
       </c>
       <c r="F51" s="0">
-        <v>7.647559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pdr</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C52" s="0">
-        <v>54.7220001220703</v>
-      </c>
-      <c r="D52" s="0">
-        <v>3672.40161132813</v>
-      </c>
-      <c r="E52" s="0">
-        <v>3727.12351244511</v>
+        <v>0</v>
       </c>
       <c r="F52" s="0">
-        <v>1.46821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>pdr</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C53" s="0">
-        <v>8.86839962005615</v>
-      </c>
-      <c r="D53" s="0">
-        <v>188.614974975586</v>
-      </c>
-      <c r="E53" s="0">
-        <v>197.483372218587</v>
+        <v>0</v>
       </c>
       <c r="F53" s="0">
-        <v>4.490707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pfb</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C54" s="0">
-        <v>-123.275497436523</v>
-      </c>
-      <c r="D54" s="0">
-        <v>3897.07495117188</v>
-      </c>
-      <c r="E54" s="0">
-        <v>3773.79940508825</v>
+        <v>0</v>
       </c>
       <c r="F54" s="0">
-        <v>-3.266615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pfb</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C55" s="0">
-        <v>-2.1768000125885</v>
-      </c>
-      <c r="D55" s="0">
-        <v>50.5459518432617</v>
-      </c>
-      <c r="E55" s="0">
-        <v>48.369152368573</v>
+        <v>0</v>
       </c>
       <c r="F55" s="0">
-        <v>-4.500389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>pfb</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C56" s="0">
-        <v>-2.57240009307861</v>
-      </c>
-      <c r="D56" s="0">
-        <v>52.0981597900391</v>
-      </c>
-      <c r="E56" s="0">
-        <v>49.5257585932909</v>
+        <v>0</v>
       </c>
       <c r="F56" s="0">
-        <v>-5.194065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>pfb</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C57" s="0">
-        <v>-514.194702148438</v>
+        <v>-131398.296875</v>
       </c>
       <c r="D57" s="0">
-        <v>10663.451171875</v>
+        <v>5159651</v>
       </c>
       <c r="E57" s="0">
-        <v>10149.2560421646</v>
+        <v>5028252.59739017</v>
       </c>
       <c r="F57" s="0">
-        <v>-5.066329</v>
+        <v>-2.6132</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>pfb</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C58" s="0">
-        <v>-5139.93017578125</v>
+        <v>-703.799987792969</v>
       </c>
       <c r="D58" s="0">
-        <v>86087.6640625</v>
+        <v>164530.609375</v>
       </c>
       <c r="E58" s="0">
-        <v>80947.7340749115</v>
+        <v>163826.81280097</v>
       </c>
       <c r="F58" s="0">
-        <v>-6.34969</v>
+        <v>-0.4296</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>pfb</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C59" s="0">
-        <v>-1188.45727539063</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="D59" s="0">
-        <v>23585.6796875</v>
+        <v>1878.72521972656</v>
       </c>
       <c r="E59" s="0">
-        <v>22397.2216155305</v>
+        <v>1885.12521218481</v>
       </c>
       <c r="F59" s="0">
-        <v>-5.306271</v>
+        <v>0.3395</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ9</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>pfb</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C60" s="0">
-        <v>-209.230194091797</v>
-      </c>
-      <c r="D60" s="0">
-        <v>11814.0078125</v>
-      </c>
-      <c r="E60" s="0">
-        <v>11604.7775771588</v>
+        <v>0</v>
       </c>
       <c r="F60" s="0">
-        <v>-1.802966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>pfb</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C61" s="0">
-        <v>-22.6284999847412</v>
-      </c>
-      <c r="D61" s="0">
-        <v>322.430969238281</v>
-      </c>
-      <c r="E61" s="0">
-        <v>299.802472119916</v>
+        <v>0</v>
       </c>
       <c r="F61" s="0">
-        <v>-7.547803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ7</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>v_f</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C62" s="0">
-        <v>-107.594596862793</v>
-      </c>
-      <c r="D62" s="0">
-        <v>153090.765625</v>
-      </c>
-      <c r="E62" s="0">
-        <v>152983.17507613</v>
+        <v>0</v>
       </c>
       <c r="F62" s="0">
-        <v>-0.070331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>v_f</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C63" s="0">
-        <v>632.723022460938</v>
+        <v>-145708.5</v>
       </c>
       <c r="D63" s="0">
-        <v>7576.03369140625</v>
+        <v>4959336</v>
       </c>
       <c r="E63" s="0">
-        <v>8208.75694025908</v>
+        <v>4813627.35381566</v>
       </c>
       <c r="F63" s="0">
-        <v>7.707903</v>
+        <v>-3.027</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>v_f</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C64" s="0">
-        <v>26.9321994781494</v>
+        <v>-250579.703125</v>
       </c>
       <c r="D64" s="0">
-        <v>361.949554443359</v>
+        <v>3712820.75</v>
       </c>
       <c r="E64" s="0">
-        <v>388.881741928791</v>
+        <v>3462241.14853195</v>
       </c>
       <c r="F64" s="0">
-        <v>6.92555</v>
+        <v>-7.2375</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>v_f</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C65" s="0">
-        <v>-1943.67028808594</v>
+        <v>-15155.099609375</v>
       </c>
       <c r="D65" s="0">
-        <v>142143.8125</v>
+        <v>3273615.5</v>
       </c>
       <c r="E65" s="0">
-        <v>140200.142826864</v>
+        <v>3258460.4621318</v>
       </c>
       <c r="F65" s="0">
-        <v>-1.386354</v>
+        <v>-0.4651</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>v_f</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C66" s="0">
-        <v>-742.823181152344</v>
+        <v>-1804.59997558594</v>
       </c>
       <c r="D66" s="0">
-        <v>243589.9375</v>
+        <v>1733666.375</v>
       </c>
       <c r="E66" s="0">
-        <v>242847.114123579</v>
+        <v>1731861.78079265</v>
       </c>
       <c r="F66" s="0">
-        <v>-0.305881</v>
+        <v>-0.1042</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>v_f</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C67" s="0">
-        <v>-250.555999755859</v>
+        <v>25370.900390625</v>
       </c>
       <c r="D67" s="0">
-        <v>194119.328125</v>
+        <v>468822.5</v>
       </c>
       <c r="E67" s="0">
-        <v>193868.771089337</v>
+        <v>494193.392625833</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.12924</v>
+        <v>5.1338</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AEZ3</t>
+          <t>AEZ1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>v_f</t>
+          <t>gro</t>
         </is>
       </c>
       <c r="C68" s="0">
-        <v>-98.4387969970703</v>
+        <v>562.599975585938</v>
       </c>
       <c r="D68" s="0">
-        <v>91871.7421875</v>
+        <v>9042.34375</v>
       </c>
       <c r="E68" s="0">
-        <v>91773.3020678802</v>
+        <v>9604.94375637548</v>
       </c>
       <c r="F68" s="0">
-        <v>-0.107263</v>
+        <v>5.8574</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AEZ2</t>
+          <t>AEZ18</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>v_f</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="C69" s="0">
-        <v>273.042694091797</v>
-      </c>
-      <c r="D69" s="0">
-        <v>6120</v>
-      </c>
-      <c r="E69" s="0">
-        <v>6393.04260289133</v>
+        <v>0</v>
       </c>
       <c r="F69" s="0">
-        <v>4.270935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AEZ12</t>
+          <t>AEZ17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>wht</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="C70" s="0">
-        <v>-8852.5869140625</v>
-      </c>
-      <c r="D70" s="0">
-        <v>215808.703125</v>
-      </c>
-      <c r="E70" s="0">
-        <v>206956.10969963</v>
+        <v>0</v>
       </c>
       <c r="F70" s="0">
-        <v>-4.277519</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AEZ11</t>
+          <t>AEZ16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>wht</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="C71" s="0">
-        <v>1.70319998264313</v>
-      </c>
-      <c r="D71" s="0">
-        <v>41.6855888366699</v>
-      </c>
-      <c r="E71" s="0">
-        <v>43.3887882738978</v>
+        <v>0</v>
       </c>
       <c r="F71" s="0">
-        <v>3.925438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AEZ10</t>
+          <t>AEZ15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>wht</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="C72" s="0">
-        <v>1.31819999217987</v>
-      </c>
-      <c r="D72" s="0">
-        <v>40.2579345703125</v>
-      </c>
-      <c r="E72" s="0">
-        <v>41.5761332486336</v>
+        <v>0</v>
       </c>
       <c r="F72" s="0">
-        <v>3.170569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AEZ6</t>
+          <t>AEZ14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>wht</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="C73" s="0">
-        <v>-2364.30541992188</v>
-      </c>
-      <c r="D73" s="0">
-        <v>69950.0078125</v>
-      </c>
-      <c r="E73" s="0">
-        <v>67585.7045520374</v>
+        <v>0</v>
       </c>
       <c r="F73" s="0">
-        <v>-3.498233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AEZ5</t>
+          <t>AEZ13</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>wht</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="C74" s="0">
-        <v>-467.648498535156</v>
-      </c>
-      <c r="D74" s="0">
-        <v>8038.70751953125</v>
-      </c>
-      <c r="E74" s="0">
-        <v>7571.0591233402</v>
+        <v>0</v>
       </c>
       <c r="F74" s="0">
-        <v>-6.176791</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AEZ4</t>
+          <t>AEZ12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>wht</t>
+          <t>ocr</t>
         </is>
       </c>
       <c r="C75" s="0">
-        <v>-27.1856994628906</v>
+        <v>283.899993896484</v>
       </c>
       <c r="D75" s="0">
-        <v>1139.30590820313</v>
+        <v>421558.59375</v>
       </c>
       <c r="E75" s="0">
-        <v>1112.12016000417</v>
+        <v>421842.487216173</v>
       </c>
       <c r="F75" s="0">
-        <v>-2.444493</v>
+        <v>0.0673</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>AEZ11</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C76" s="0">
+        <v>44.2999992370605</v>
+      </c>
+      <c r="D76" s="0">
+        <v>107741.5859375</v>
+      </c>
+      <c r="E76" s="0">
+        <v>107785.886221559</v>
+      </c>
+      <c r="F76" s="0">
+        <v>0.0411</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AEZ10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C77" s="0">
+        <v>-349.700012207031</v>
+      </c>
+      <c r="D77" s="0">
+        <v>7308.48876953125</v>
+      </c>
+      <c r="E77" s="0">
+        <v>6958.7887729495</v>
+      </c>
+      <c r="F77" s="0">
+        <v>-5.0253</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>AEZ9</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C78" s="0">
+        <v>0</v>
+      </c>
+      <c r="F78" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AEZ8</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C79" s="0">
+        <v>0</v>
+      </c>
+      <c r="F79" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AEZ7</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C80" s="0">
+        <v>0</v>
+      </c>
+      <c r="F80" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AEZ6</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C81" s="0">
+        <v>-14496.599609375</v>
+      </c>
+      <c r="D81" s="0">
+        <v>830287.25</v>
+      </c>
+      <c r="E81" s="0">
+        <v>815790.636430782</v>
+      </c>
+      <c r="F81" s="0">
+        <v>-1.777</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AEZ5</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C82" s="0">
+        <v>4809</v>
+      </c>
+      <c r="D82" s="0">
+        <v>1079764.75</v>
+      </c>
+      <c r="E82" s="0">
+        <v>1084573.74830852</v>
+      </c>
+      <c r="F82" s="0">
+        <v>0.4434</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>AEZ4</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C83" s="0">
+        <v>714.900024414063</v>
+      </c>
+      <c r="D83" s="0">
+        <v>301058</v>
+      </c>
+      <c r="E83" s="0">
+        <v>301772.910263429</v>
+      </c>
+      <c r="F83" s="0">
+        <v>0.2369</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>AEZ3</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C84" s="0">
+        <v>4.40000009536743</v>
+      </c>
+      <c r="D84" s="0">
+        <v>95647.7734375</v>
+      </c>
+      <c r="E84" s="0">
+        <v>95652.1759862485</v>
+      </c>
+      <c r="F84" s="0">
+        <v>0.0046</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AEZ2</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C85" s="0">
+        <v>-174.399993896484</v>
+      </c>
+      <c r="D85" s="0">
+        <v>35956.09765625</v>
+      </c>
+      <c r="E85" s="0">
+        <v>35781.6975577522</v>
+      </c>
+      <c r="F85" s="0">
+        <v>-0.4874</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>AEZ1</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C86" s="0">
+        <v>1.5</v>
+      </c>
+      <c r="D86" s="0">
+        <v>757.99365234375</v>
+      </c>
+      <c r="E86" s="0">
+        <v>759.493670886076</v>
+      </c>
+      <c r="F86" s="0">
+        <v>0.1975</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AEZ18</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C87" s="0">
+        <v>0</v>
+      </c>
+      <c r="F87" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AEZ17</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C88" s="0">
+        <v>0</v>
+      </c>
+      <c r="F88" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AEZ16</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C89" s="0">
+        <v>0</v>
+      </c>
+      <c r="F89" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>AEZ15</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C90" s="0">
+        <v>0</v>
+      </c>
+      <c r="F90" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AEZ14</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C91" s="0">
+        <v>0</v>
+      </c>
+      <c r="F91" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AEZ13</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C92" s="0">
+        <v>0</v>
+      </c>
+      <c r="F92" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>AEZ12</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C93" s="0">
+        <v>-434223.40625</v>
+      </c>
+      <c r="D93" s="0">
+        <v>10124115</v>
+      </c>
+      <c r="E93" s="0">
+        <v>9689891.24006962</v>
+      </c>
+      <c r="F93" s="0">
+        <v>-4.4812</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AEZ11</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C94" s="0">
+        <v>-109.5</v>
+      </c>
+      <c r="D94" s="0">
+        <v>13903.90625</v>
+      </c>
+      <c r="E94" s="0">
+        <v>13794.4066515495</v>
+      </c>
+      <c r="F94" s="0">
+        <v>-0.7938</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AEZ10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C95" s="0">
+        <v>-25.5</v>
+      </c>
+      <c r="D95" s="0">
+        <v>394.066345214844</v>
+      </c>
+      <c r="E95" s="0">
+        <v>368.566349169642</v>
+      </c>
+      <c r="F95" s="0">
+        <v>-6.9187</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AEZ9</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C96" s="0">
+        <v>0</v>
+      </c>
+      <c r="F96" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AEZ8</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C97" s="0">
+        <v>0</v>
+      </c>
+      <c r="F97" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AEZ7</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C98" s="0">
+        <v>0</v>
+      </c>
+      <c r="F98" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AEZ6</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C99" s="0">
+        <v>-265975.5</v>
+      </c>
+      <c r="D99" s="0">
+        <v>8409994</v>
+      </c>
+      <c r="E99" s="0">
+        <v>8144018.49413638</v>
+      </c>
+      <c r="F99" s="0">
+        <v>-3.2659</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AEZ5</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C100" s="0">
+        <v>-781123.5</v>
+      </c>
+      <c r="D100" s="0">
+        <v>8991291</v>
+      </c>
+      <c r="E100" s="0">
+        <v>8210167.01527207</v>
+      </c>
+      <c r="F100" s="0">
+        <v>-9.5141</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>AEZ4</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C101" s="0">
+        <v>-62606.80078125</v>
+      </c>
+      <c r="D101" s="0">
+        <v>10474514</v>
+      </c>
+      <c r="E101" s="0">
+        <v>10411907.6636039</v>
+      </c>
+      <c r="F101" s="0">
+        <v>-0.6013</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AEZ3</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C102" s="0">
+        <v>-692.299987792969</v>
+      </c>
+      <c r="D102" s="0">
+        <v>274112.53125</v>
+      </c>
+      <c r="E102" s="0">
+        <v>273420.216347934</v>
+      </c>
+      <c r="F102" s="0">
+        <v>-0.2532</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>AEZ2</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C103" s="0">
+        <v>-1488.69995117188</v>
+      </c>
+      <c r="D103" s="0">
+        <v>61728.24609375</v>
+      </c>
+      <c r="E103" s="0">
+        <v>60239.5480585876</v>
+      </c>
+      <c r="F103" s="0">
+        <v>-2.4713</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AEZ1</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>osd</t>
+        </is>
+      </c>
+      <c r="C104" s="0">
+        <v>-77.4000015258789</v>
+      </c>
+      <c r="D104" s="0">
+        <v>4377.39990234375</v>
+      </c>
+      <c r="E104" s="0">
+        <v>4300.00008477105</v>
+      </c>
+      <c r="F104" s="0">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AEZ18</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C105" s="0">
+        <v>0</v>
+      </c>
+      <c r="F105" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AEZ17</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C106" s="0">
+        <v>0</v>
+      </c>
+      <c r="F106" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AEZ16</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C107" s="0">
+        <v>0</v>
+      </c>
+      <c r="F107" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AEZ15</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C108" s="0">
+        <v>0</v>
+      </c>
+      <c r="F108" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AEZ14</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C109" s="0">
+        <v>0</v>
+      </c>
+      <c r="F109" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AEZ13</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C110" s="0">
+        <v>0</v>
+      </c>
+      <c r="F110" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AEZ12</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C111" s="0">
+        <v>52518.3984375</v>
+      </c>
+      <c r="D111" s="0">
+        <v>600654.875</v>
+      </c>
+      <c r="E111" s="0">
+        <v>653173.290684659</v>
+      </c>
+      <c r="F111" s="0">
+        <v>8.0405</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AEZ11</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C112" s="0">
+        <v>-106.099998474121</v>
+      </c>
+      <c r="D112" s="0">
+        <v>4028.90087890625</v>
+      </c>
+      <c r="E112" s="0">
+        <v>3922.8009936082</v>
+      </c>
+      <c r="F112" s="0">
+        <v>-2.7047</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>AEZ10</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C113" s="0">
+        <v>1.79999995231628</v>
+      </c>
+      <c r="D113" s="0">
+        <v>71.4779663085938</v>
+      </c>
+      <c r="E113" s="0">
+        <v>73.277965816491</v>
+      </c>
+      <c r="F113" s="0">
+        <v>2.4564</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>AEZ9</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C114" s="0">
+        <v>0</v>
+      </c>
+      <c r="F114" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AEZ8</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C115" s="0">
+        <v>0</v>
+      </c>
+      <c r="F115" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>AEZ7</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C116" s="0">
+        <v>0</v>
+      </c>
+      <c r="F116" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>AEZ6</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C117" s="0">
+        <v>-34202.80078125</v>
+      </c>
+      <c r="D117" s="0">
+        <v>190134.328125</v>
+      </c>
+      <c r="E117" s="0">
+        <v>155931.526960952</v>
+      </c>
+      <c r="F117" s="0">
+        <v>-21.9345</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>AEZ5</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C118" s="0">
+        <v>-8918.900390625</v>
+      </c>
+      <c r="D118" s="0">
+        <v>314078.53125</v>
+      </c>
+      <c r="E118" s="0">
+        <v>305159.626052109</v>
+      </c>
+      <c r="F118" s="0">
+        <v>-2.9227</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AEZ4</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C119" s="0">
+        <v>-19518.099609375</v>
+      </c>
+      <c r="D119" s="0">
+        <v>534657.0625</v>
+      </c>
+      <c r="E119" s="0">
+        <v>515138.948227058</v>
+      </c>
+      <c r="F119" s="0">
+        <v>-3.7889</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AEZ3</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C120" s="0">
+        <v>-3703.10009765625</v>
+      </c>
+      <c r="D120" s="0">
+        <v>73650.78125</v>
+      </c>
+      <c r="E120" s="0">
+        <v>69947.679447994</v>
+      </c>
+      <c r="F120" s="0">
+        <v>-5.2941</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>AEZ2</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C121" s="0">
+        <v>477.799987792969</v>
+      </c>
+      <c r="D121" s="0">
+        <v>6021.28857421875</v>
+      </c>
+      <c r="E121" s="0">
+        <v>6499.08849251841</v>
+      </c>
+      <c r="F121" s="0">
+        <v>7.3518</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AEZ1</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>pdr</t>
+        </is>
+      </c>
+      <c r="C122" s="0">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="D122" s="0">
+        <v>205.613647460938</v>
+      </c>
+      <c r="E122" s="0">
+        <v>223.713651247355</v>
+      </c>
+      <c r="F122" s="0">
+        <v>8.0907</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AEZ18</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C123" s="0">
+        <v>0</v>
+      </c>
+      <c r="F123" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>AEZ17</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C124" s="0">
+        <v>0</v>
+      </c>
+      <c r="F124" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AEZ16</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C125" s="0">
+        <v>0</v>
+      </c>
+      <c r="F125" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>AEZ15</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C126" s="0">
+        <v>0</v>
+      </c>
+      <c r="F126" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AEZ14</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C127" s="0">
+        <v>0</v>
+      </c>
+      <c r="F127" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>AEZ13</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C128" s="0">
+        <v>0</v>
+      </c>
+      <c r="F128" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AEZ12</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C129" s="0">
+        <v>-1052.90002441406</v>
+      </c>
+      <c r="D129" s="0">
+        <v>24027.435546875</v>
+      </c>
+      <c r="E129" s="0">
+        <v>22974.5363070122</v>
+      </c>
+      <c r="F129" s="0">
+        <v>-4.5829</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AEZ11</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C130" s="0">
+        <v>-12.1000003814697</v>
+      </c>
+      <c r="D130" s="0">
+        <v>1512.0380859375</v>
+      </c>
+      <c r="E130" s="0">
+        <v>1499.9380663778</v>
+      </c>
+      <c r="F130" s="0">
+        <v>-0.8067</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>AEZ10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C131" s="0">
+        <v>-77</v>
+      </c>
+      <c r="D131" s="0">
+        <v>887.321594238281</v>
+      </c>
+      <c r="E131" s="0">
+        <v>810.321602963462</v>
+      </c>
+      <c r="F131" s="0">
+        <v>-9.5024</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>AEZ9</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C132" s="0">
+        <v>0</v>
+      </c>
+      <c r="F132" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>AEZ8</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C133" s="0">
+        <v>0</v>
+      </c>
+      <c r="F133" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>AEZ7</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C134" s="0">
+        <v>0</v>
+      </c>
+      <c r="F134" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>AEZ6</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C135" s="0">
+        <v>-7497.2001953125</v>
+      </c>
+      <c r="D135" s="0">
+        <v>162776.609375</v>
+      </c>
+      <c r="E135" s="0">
+        <v>155279.404235792</v>
+      </c>
+      <c r="F135" s="0">
+        <v>-4.8282</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>AEZ5</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C136" s="0">
+        <v>-60349</v>
+      </c>
+      <c r="D136" s="0">
+        <v>611844.0625</v>
+      </c>
+      <c r="E136" s="0">
+        <v>551495.046971525</v>
+      </c>
+      <c r="F136" s="0">
+        <v>-10.9428</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>AEZ4</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C137" s="0">
+        <v>-12829.400390625</v>
+      </c>
+      <c r="D137" s="0">
+        <v>771516.5625</v>
+      </c>
+      <c r="E137" s="0">
+        <v>758687.19045683</v>
+      </c>
+      <c r="F137" s="0">
+        <v>-1.691</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AEZ3</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C138" s="0">
+        <v>-1687.19995117188</v>
+      </c>
+      <c r="D138" s="0">
+        <v>152545.5625</v>
+      </c>
+      <c r="E138" s="0">
+        <v>150858.364732821</v>
+      </c>
+      <c r="F138" s="0">
+        <v>-1.1184</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>AEZ2</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C139" s="0">
+        <v>-4965.7001953125</v>
+      </c>
+      <c r="D139" s="0">
+        <v>100860.109375</v>
+      </c>
+      <c r="E139" s="0">
+        <v>95894.4092716239</v>
+      </c>
+      <c r="F139" s="0">
+        <v>-5.1783</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>AEZ1</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>pfb</t>
+        </is>
+      </c>
+      <c r="C140" s="0">
+        <v>-498</v>
+      </c>
+      <c r="D140" s="0">
+        <v>11501.822265625</v>
+      </c>
+      <c r="E140" s="0">
+        <v>11003.8226130764</v>
+      </c>
+      <c r="F140" s="0">
+        <v>-4.5257</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AEZ18</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C141" s="0">
+        <v>0</v>
+      </c>
+      <c r="F141" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AEZ17</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C142" s="0">
+        <v>0</v>
+      </c>
+      <c r="F142" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AEZ16</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C143" s="0">
+        <v>0</v>
+      </c>
+      <c r="F143" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>AEZ15</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C144" s="0">
+        <v>0</v>
+      </c>
+      <c r="F144" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AEZ14</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C145" s="0">
+        <v>0</v>
+      </c>
+      <c r="F145" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AEZ13</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C146" s="0">
+        <v>0</v>
+      </c>
+      <c r="F146" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AEZ12</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C147" s="0">
+        <v>-4690.39990234375</v>
+      </c>
+      <c r="D147" s="0">
+        <v>1045382.625</v>
+      </c>
+      <c r="E147" s="0">
+        <v>1040692.23482222</v>
+      </c>
+      <c r="F147" s="0">
+        <v>-0.4507</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>AEZ11</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C148" s="0">
+        <v>-40.2999992370605</v>
+      </c>
+      <c r="D148" s="0">
+        <v>46415.44140625</v>
+      </c>
+      <c r="E148" s="0">
+        <v>46375.1429655472</v>
+      </c>
+      <c r="F148" s="0">
+        <v>-0.0869</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>AEZ10</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C149" s="0">
+        <v>326.399993896484</v>
+      </c>
+      <c r="D149" s="0">
+        <v>5301.18603515625</v>
+      </c>
+      <c r="E149" s="0">
+        <v>5627.58610166352</v>
+      </c>
+      <c r="F149" s="0">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>AEZ9</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C150" s="0">
+        <v>0</v>
+      </c>
+      <c r="F150" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AEZ8</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C151" s="0">
+        <v>0</v>
+      </c>
+      <c r="F151" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>AEZ7</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C152" s="0">
+        <v>0</v>
+      </c>
+      <c r="F152" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>AEZ6</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C153" s="0">
+        <v>-23355.099609375</v>
+      </c>
+      <c r="D153" s="0">
+        <v>1222159.125</v>
+      </c>
+      <c r="E153" s="0">
+        <v>1198804.00417693</v>
+      </c>
+      <c r="F153" s="0">
+        <v>-1.9482</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>AEZ5</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C154" s="0">
+        <v>-5807.7001953125</v>
+      </c>
+      <c r="D154" s="0">
+        <v>1392886.75</v>
+      </c>
+      <c r="E154" s="0">
+        <v>1387079.10086279</v>
+      </c>
+      <c r="F154" s="0">
+        <v>-0.4187</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>AEZ4</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C155" s="0">
+        <v>1962.5</v>
+      </c>
+      <c r="D155" s="0">
+        <v>1500717.5</v>
+      </c>
+      <c r="E155" s="0">
+        <v>1502679.93874426</v>
+      </c>
+      <c r="F155" s="0">
+        <v>0.1306</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>AEZ3</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C156" s="0">
+        <v>-918.900024414063</v>
+      </c>
+      <c r="D156" s="0">
+        <v>1393191.625</v>
+      </c>
+      <c r="E156" s="0">
+        <v>1392272.76426373</v>
+      </c>
+      <c r="F156" s="0">
+        <v>-0.066</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>AEZ2</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C157" s="0">
+        <v>55158.6015625</v>
+      </c>
+      <c r="D157" s="0">
+        <v>452976.75</v>
+      </c>
+      <c r="E157" s="0">
+        <v>508135.360913303</v>
+      </c>
+      <c r="F157" s="0">
+        <v>10.8551</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>AEZ1</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>v_f</t>
+        </is>
+      </c>
+      <c r="C158" s="0">
+        <v>2526.69995117188</v>
+      </c>
+      <c r="D158" s="0">
+        <v>19221.26171875</v>
+      </c>
+      <c r="E158" s="0">
+        <v>21747.9618110696</v>
+      </c>
+      <c r="F158" s="0">
+        <v>11.6181</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>AEZ18</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
         <is>
           <t>wht</t>
         </is>
       </c>
-      <c r="C76" s="0">
-        <v>-0.362500011920929</v>
-      </c>
-      <c r="D76" s="0">
-        <v>184.69921875</v>
-      </c>
-      <c r="E76" s="0">
-        <v>184.336724410722</v>
-      </c>
-      <c r="F76" s="0">
-        <v>-0.196651</v>
+      <c r="C159" s="0">
+        <v>0</v>
+      </c>
+      <c r="F159" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>AEZ17</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C160" s="0">
+        <v>0</v>
+      </c>
+      <c r="F160" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>AEZ16</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C161" s="0">
+        <v>0</v>
+      </c>
+      <c r="F161" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>AEZ15</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C162" s="0">
+        <v>0</v>
+      </c>
+      <c r="F162" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>AEZ14</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C163" s="0">
+        <v>0</v>
+      </c>
+      <c r="F163" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>AEZ13</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C164" s="0">
+        <v>0</v>
+      </c>
+      <c r="F164" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>AEZ12</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C165" s="0">
+        <v>-68492.703125</v>
+      </c>
+      <c r="D165" s="0">
+        <v>1237330.125</v>
+      </c>
+      <c r="E165" s="0">
+        <v>1168837.4055018</v>
+      </c>
+      <c r="F165" s="0">
+        <v>-5.8599</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>AEZ11</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C166" s="0">
+        <v>-9.80000019073486</v>
+      </c>
+      <c r="D166" s="0">
+        <v>728.380432128906</v>
+      </c>
+      <c r="E166" s="0">
+        <v>718.58045099977</v>
+      </c>
+      <c r="F166" s="0">
+        <v>-1.3638</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>AEZ10</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C167" s="0">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="D167" s="0">
+        <v>401.004577636719</v>
+      </c>
+      <c r="E167" s="0">
+        <v>415.404575754515</v>
+      </c>
+      <c r="F167" s="0">
+        <v>3.4665</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>AEZ9</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C168" s="0">
+        <v>0</v>
+      </c>
+      <c r="F168" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>AEZ8</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C169" s="0">
+        <v>0</v>
+      </c>
+      <c r="F169" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>AEZ7</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C170" s="0">
+        <v>0</v>
+      </c>
+      <c r="F170" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>AEZ6</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C171" s="0">
+        <v>-29851.599609375</v>
+      </c>
+      <c r="D171" s="0">
+        <v>890574.75</v>
+      </c>
+      <c r="E171" s="0">
+        <v>860723.130424284</v>
+      </c>
+      <c r="F171" s="0">
+        <v>-3.4682</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>AEZ5</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C172" s="0">
+        <v>-3666.89990234375</v>
+      </c>
+      <c r="D172" s="0">
+        <v>37009.9296875</v>
+      </c>
+      <c r="E172" s="0">
+        <v>33343.0316194021</v>
+      </c>
+      <c r="F172" s="0">
+        <v>-10.9975</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>AEZ4</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C173" s="0">
+        <v>-184.699996948242</v>
+      </c>
+      <c r="D173" s="0">
+        <v>31190.23828125</v>
+      </c>
+      <c r="E173" s="0">
+        <v>31005.5391888941</v>
+      </c>
+      <c r="F173" s="0">
+        <v>-0.5957</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>AEZ3</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C174" s="0">
+        <v>-5.40000009536743</v>
+      </c>
+      <c r="D174" s="0">
+        <v>4910.0322265625</v>
+      </c>
+      <c r="E174" s="0">
+        <v>4904.63223920748</v>
+      </c>
+      <c r="F174" s="0">
+        <v>-0.1101</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>AEZ2</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>wht</t>
+        </is>
+      </c>
+      <c r="C175" s="0">
+        <v>303.299987792969</v>
+      </c>
+      <c r="D175" s="0">
+        <v>3303.07788085938</v>
+      </c>
+      <c r="E175" s="0">
+        <v>3606.37790029808</v>
+      </c>
+      <c r="F175" s="0">
+        <v>8.4101</v>
       </c>
     </row>
   </sheetData>
